--- a/data/trans_orig/P05A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289727</t>
+          <t>288462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351002</t>
+          <t>350176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385987</t>
+          <t>386539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>452204</t>
+          <t>452236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>692306</t>
+          <t>690145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>786187</t>
+          <t>778159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474011</t>
+          <t>470741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>537259</t>
+          <t>538713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>597469</t>
+          <t>593452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670580</t>
+          <t>665401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090046</t>
+          <t>1090564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1184518</t>
+          <t>1185568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179570</t>
+          <t>178780</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230405</t>
+          <t>230023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>232083</t>
+          <t>233717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>291573</t>
+          <t>296892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>423995</t>
+          <t>425205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>501280</t>
+          <t>497450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560591</t>
+          <t>560970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>638639</t>
+          <t>640517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464676</t>
+          <t>464730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>542044</t>
+          <t>540787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1038990</t>
+          <t>1049551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1149871</t>
+          <t>1154368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>758312</t>
+          <t>761651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>842595</t>
+          <t>844567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>738284</t>
+          <t>739692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819620</t>
+          <t>822372</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1531297</t>
+          <t>1527544</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1642819</t>
+          <t>1642277</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259046</t>
+          <t>257739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>321430</t>
+          <t>324984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>271478</t>
+          <t>269118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>333230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>549934</t>
+          <t>547235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>636416</t>
+          <t>635581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133817</t>
+          <t>133509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178939</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111596</t>
+          <t>110763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150508</t>
+          <t>151975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>254948</t>
+          <t>255903</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>312639</t>
+          <t>315362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267701</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314544</t>
+          <t>314596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237366</t>
+          <t>236988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281985</t>
+          <t>280856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>519105</t>
+          <t>516436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>585276</t>
+          <t>584365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>120849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>69795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103497</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161804</t>
+          <t>161758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212922</t>
+          <t>212727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1022118</t>
+          <t>1020819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1128639</t>
+          <t>1132825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>995094</t>
+          <t>993982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1106850</t>
+          <t>1104160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2045308</t>
+          <t>2048112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2201402</t>
+          <t>2193004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1537180</t>
+          <t>1540307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1660123</t>
+          <t>1657325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1618564</t>
+          <t>1614570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1729902</t>
+          <t>1729953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3192424</t>
+          <t>3184798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3363682</t>
+          <t>3357488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>550722</t>
+          <t>549875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639030</t>
+          <t>641177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>598882</t>
+          <t>603895</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>694705</t>
+          <t>690548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1178313</t>
+          <t>1174107</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1300924</t>
+          <t>1310400</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266112</t>
+          <t>266399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324980</t>
+          <t>325050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354432</t>
+          <t>353649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>423066</t>
+          <t>420614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638188</t>
+          <t>635058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>727874</t>
+          <t>732981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405579</t>
+          <t>404910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469814</t>
+          <t>467459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>581519</t>
+          <t>578998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>654065</t>
+          <t>650845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1009424</t>
+          <t>1004728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1106801</t>
+          <t>1106645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206596</t>
+          <t>209487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>262392</t>
+          <t>263024</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>294444</t>
+          <t>290402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>357190</t>
+          <t>354986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>517488</t>
+          <t>517147</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>604212</t>
+          <t>599409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>623305</t>
+          <t>623741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>708055</t>
+          <t>710254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599927</t>
+          <t>597177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>680031</t>
+          <t>680560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1249792</t>
+          <t>1246091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1365346</t>
+          <t>1360787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>757582</t>
+          <t>756454</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>844865</t>
+          <t>845932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>659287</t>
+          <t>657660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>739421</t>
+          <t>742081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1437600</t>
+          <t>1440248</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1556463</t>
+          <t>1567646</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>451423</t>
+          <t>452216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>532462</t>
+          <t>528137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>370627</t>
+          <t>375866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447090</t>
+          <t>446875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>849616</t>
+          <t>848803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>952140</t>
+          <t>950803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116057</t>
+          <t>117172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158835</t>
+          <t>158379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117972</t>
+          <t>119012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160003</t>
+          <t>162048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>244493</t>
+          <t>245528</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>305795</t>
+          <t>307711</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191595</t>
+          <t>189631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239052</t>
+          <t>237006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177074</t>
+          <t>176895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222973</t>
+          <t>220527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380268</t>
+          <t>380335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>445159</t>
+          <t>444555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109647</t>
+          <t>110574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152740</t>
+          <t>153176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99679</t>
+          <t>101041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141843</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221466</t>
+          <t>221577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281256</t>
+          <t>277565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1046087</t>
+          <t>1038424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1157511</t>
+          <t>1157472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1107011</t>
+          <t>1106270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1225696</t>
+          <t>1221492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2183035</t>
+          <t>2195046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2338699</t>
+          <t>2348920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1389509</t>
+          <t>1387078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1511562</t>
+          <t>1510508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1451996</t>
+          <t>1450770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1573733</t>
+          <t>1572487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2881259</t>
+          <t>2878126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3045860</t>
+          <t>3039779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>800169</t>
+          <t>804847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>906860</t>
+          <t>906119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>809038</t>
+          <t>805810</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>904559</t>
+          <t>904999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1634450</t>
+          <t>1637678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1783554</t>
+          <t>1780844</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278364</t>
+          <t>278227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331147</t>
+          <t>330014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381044</t>
+          <t>380092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>446460</t>
+          <t>444952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>675074</t>
+          <t>675617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>757185</t>
+          <t>756026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257232</t>
+          <t>252883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308231</t>
+          <t>305155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>348467</t>
+          <t>350731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412064</t>
+          <t>411702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>621104</t>
+          <t>617917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>701641</t>
+          <t>698523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147589</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191248</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171105</t>
+          <t>170943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220161</t>
+          <t>223644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>329756</t>
+          <t>332099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>405336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>729152</t>
+          <t>729580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>817061</t>
+          <t>819258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753917</t>
+          <t>749823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>838298</t>
+          <t>839543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1511471</t>
+          <t>1501080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1631860</t>
+          <t>1630715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>778676</t>
+          <t>783183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>870090</t>
+          <t>874603</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>709541</t>
+          <t>707965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>798151</t>
+          <t>794926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1515075</t>
+          <t>1516626</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1642030</t>
+          <t>1642604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>431090</t>
+          <t>427865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508682</t>
+          <t>509230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397619</t>
+          <t>395884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>476193</t>
+          <t>469190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848898</t>
+          <t>847973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>956691</t>
+          <t>957735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159304</t>
+          <t>156635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203662</t>
+          <t>202680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174063</t>
+          <t>175129</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218145</t>
+          <t>218291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>345480</t>
+          <t>341709</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>407723</t>
+          <t>405152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198167</t>
+          <t>196780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>247383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195936</t>
+          <t>195276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241691</t>
+          <t>242594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409301</t>
+          <t>410078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>474051</t>
+          <t>475059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>120943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167209</t>
+          <t>164205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114953</t>
+          <t>114553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154809</t>
+          <t>155008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>251713</t>
+          <t>249089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305851</t>
+          <t>308046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1200372</t>
+          <t>1201334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1314232</t>
+          <t>1310130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1344661</t>
+          <t>1349259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1458427</t>
+          <t>1465325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2579186</t>
+          <t>2585730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2750904</t>
+          <t>2746272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1266295</t>
+          <t>1276421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1386028</t>
+          <t>1390836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1288611</t>
+          <t>1289638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1406297</t>
+          <t>1411517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2592169</t>
+          <t>2605280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2766388</t>
+          <t>2765041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>727463</t>
+          <t>727251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>827942</t>
+          <t>827426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>722006</t>
+          <t>714665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>814875</t>
+          <t>814041</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1468650</t>
+          <t>1474360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1613743</t>
+          <t>1607125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>69584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68943</t>
+          <t>69543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95539</t>
+          <t>95427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131513</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>44757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67779</t>
+          <t>68825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>105048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137202</t>
+          <t>135161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,17 +7076,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>174177</t>
+          <t>174176</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155115</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194180</t>
+          <t>195750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>386042</t>
+          <t>385382</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>420458</t>
+          <t>419159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>555211</t>
+          <t>555837</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>592346</t>
+          <t>592930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,17 +7189,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>978476</t>
+          <t>978475</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>953454</t>
+          <t>953413</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1003470</t>
+          <t>1003097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1265389</t>
+          <t>1265388</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1265389</t>
+          <t>1265388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1265389</t>
+          <t>1265388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91530</t>
+          <t>95929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177833</t>
+          <t>175277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893508</t>
+          <t>826203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304940</t>
+          <t>301558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1195175</t>
+          <t>1169920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173571</t>
+          <t>176854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>301399</t>
+          <t>306202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>230401</t>
+          <t>229511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>540035</t>
+          <t>519425</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>466545</t>
+          <t>460679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>775083</t>
+          <t>785723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1834339</t>
+          <t>1831077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026805</t>
+          <t>2018253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1126176</t>
+          <t>1099309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1748093</t>
+          <t>1738608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2882425</t>
+          <t>2925799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3669103</t>
+          <t>3673477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56182</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>92468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65950</t>
+          <t>65245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95146</t>
+          <t>95824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132312</t>
+          <t>131163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176780</t>
+          <t>177939</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88569</t>
+          <t>88013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>132744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>81905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113988</t>
+          <t>113837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179287</t>
+          <t>179398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231598</t>
+          <t>232848</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>440546</t>
+          <t>438720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>487819</t>
+          <t>488169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>460701</t>
+          <t>461326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>500924</t>
+          <t>501151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>913185</t>
+          <t>915510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>979099</t>
+          <t>977571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>204843</t>
+          <t>205458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>307937</t>
+          <t>307743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312013</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1094387</t>
+          <t>1205504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>566921</t>
+          <t>566079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1450233</t>
+          <t>1452015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322098</t>
+          <t>324401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469302</t>
+          <t>467559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>443425</t>
+          <t>451800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>763739</t>
+          <t>761253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836934</t>
+          <t>836450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160970</t>
+          <t>1152443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2694537</t>
+          <t>2696452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2928888</t>
+          <t>2932636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2109058</t>
+          <t>2056461</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2792160</t>
+          <t>2806062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4768693</t>
+          <t>4816256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5587831</t>
+          <t>5593246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>288462</t>
+          <t>288865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350176</t>
+          <t>352170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>386539</t>
+          <t>388503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>452236</t>
+          <t>453064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>690145</t>
+          <t>690703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>778159</t>
+          <t>786300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>470741</t>
+          <t>472888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>538713</t>
+          <t>537722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>593452</t>
+          <t>598395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>665401</t>
+          <t>667600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090564</t>
+          <t>1088206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1185568</t>
+          <t>1188191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178780</t>
+          <t>177991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230023</t>
+          <t>228722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>233717</t>
+          <t>233600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>296892</t>
+          <t>290301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>425205</t>
+          <t>424074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>497450</t>
+          <t>499664</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560970</t>
+          <t>557355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>640517</t>
+          <t>639120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464730</t>
+          <t>463957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540787</t>
+          <t>534378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1049551</t>
+          <t>1046665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1154368</t>
+          <t>1152690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>761651</t>
+          <t>760106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>844567</t>
+          <t>845155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>739692</t>
+          <t>743931</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>822372</t>
+          <t>824112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1527544</t>
+          <t>1528344</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1642277</t>
+          <t>1644807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257739</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324984</t>
+          <t>324454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269118</t>
+          <t>270644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333230</t>
+          <t>331646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>547235</t>
+          <t>545884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>635581</t>
+          <t>632590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133509</t>
+          <t>133399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175887</t>
+          <t>176340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110763</t>
+          <t>111209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151975</t>
+          <t>151087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>255903</t>
+          <t>253609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>315362</t>
+          <t>314875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267599</t>
+          <t>268768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314596</t>
+          <t>316844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236988</t>
+          <t>238166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280856</t>
+          <t>282587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>516436</t>
+          <t>520181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584365</t>
+          <t>586165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>83162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120849</t>
+          <t>121143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69795</t>
+          <t>70217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>103919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161758</t>
+          <t>162968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212727</t>
+          <t>211730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1020819</t>
+          <t>1019364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1132825</t>
+          <t>1121126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>998673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1104160</t>
+          <t>1107392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2048112</t>
+          <t>2046207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2193004</t>
+          <t>2196875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1540307</t>
+          <t>1543587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1657325</t>
+          <t>1657056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1614570</t>
+          <t>1615658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1729953</t>
+          <t>1728967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3184798</t>
+          <t>3192964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3357488</t>
+          <t>3351784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>549875</t>
+          <t>554313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>641177</t>
+          <t>639575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>603895</t>
+          <t>604021</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>690548</t>
+          <t>691230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1174107</t>
+          <t>1181043</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310400</t>
+          <t>1301389</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266399</t>
+          <t>266715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325050</t>
+          <t>326994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353649</t>
+          <t>356675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>420614</t>
+          <t>424804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635058</t>
+          <t>639914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>732981</t>
+          <t>728343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404910</t>
+          <t>403209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467459</t>
+          <t>468158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578998</t>
+          <t>578876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650845</t>
+          <t>654477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1004728</t>
+          <t>1005649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1106645</t>
+          <t>1099449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209487</t>
+          <t>207936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263024</t>
+          <t>262469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>290402</t>
+          <t>294022</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>354986</t>
+          <t>356115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>517147</t>
+          <t>518070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599409</t>
+          <t>605812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>623741</t>
+          <t>624656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>710254</t>
+          <t>712277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597177</t>
+          <t>595156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>680560</t>
+          <t>677483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1246091</t>
+          <t>1244267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360787</t>
+          <t>1364045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>756454</t>
+          <t>751993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>845932</t>
+          <t>841575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>657660</t>
+          <t>657365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>742081</t>
+          <t>742308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1440248</t>
+          <t>1441908</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1567646</t>
+          <t>1566535</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>452216</t>
+          <t>451821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>528137</t>
+          <t>533071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375866</t>
+          <t>377451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>448796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848803</t>
+          <t>851006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>950803</t>
+          <t>954247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>114970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>157533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119012</t>
+          <t>118081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162048</t>
+          <t>162613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>245528</t>
+          <t>245114</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307711</t>
+          <t>304929</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189631</t>
+          <t>190255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237006</t>
+          <t>240169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176895</t>
+          <t>175857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220527</t>
+          <t>220251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380335</t>
+          <t>379484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444555</t>
+          <t>445842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110574</t>
+          <t>110264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153176</t>
+          <t>151667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101041</t>
+          <t>100442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141811</t>
+          <t>140976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221577</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277565</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1038424</t>
+          <t>1043039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1157472</t>
+          <t>1159646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1106270</t>
+          <t>1109929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1221492</t>
+          <t>1221237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2195046</t>
+          <t>2183060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2348920</t>
+          <t>2339688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1387078</t>
+          <t>1395432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1510508</t>
+          <t>1514209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1450770</t>
+          <t>1450150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1572487</t>
+          <t>1572625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2878126</t>
+          <t>2873497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3039779</t>
+          <t>3048817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>804847</t>
+          <t>803414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>906119</t>
+          <t>908590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>805810</t>
+          <t>803480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>904999</t>
+          <t>911533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637678</t>
+          <t>1637772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1780844</t>
+          <t>1788480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>278227</t>
+          <t>277267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>330014</t>
+          <t>328982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>380092</t>
+          <t>381088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444952</t>
+          <t>445087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>675617</t>
+          <t>674961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>756026</t>
+          <t>755796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252883</t>
+          <t>257329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305155</t>
+          <t>306914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350731</t>
+          <t>349976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>411702</t>
+          <t>411715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617917</t>
+          <t>618614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698523</t>
+          <t>699466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>146337</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191182</t>
+          <t>190766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170943</t>
+          <t>169493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223644</t>
+          <t>223631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>332099</t>
+          <t>328603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>405336</t>
+          <t>399341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>729580</t>
+          <t>733126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>819258</t>
+          <t>818638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749823</t>
+          <t>749945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>839543</t>
+          <t>833728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1501080</t>
+          <t>1502390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1630715</t>
+          <t>1628299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>783183</t>
+          <t>776647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>874603</t>
+          <t>866615</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>707965</t>
+          <t>710237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>794926</t>
+          <t>793075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1516626</t>
+          <t>1519036</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1642604</t>
+          <t>1638718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>427865</t>
+          <t>430641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>509230</t>
+          <t>509159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>395884</t>
+          <t>397300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>469190</t>
+          <t>473772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>847973</t>
+          <t>853260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>957735</t>
+          <t>964679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>156635</t>
+          <t>156780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>202680</t>
+          <t>203561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175129</t>
+          <t>175616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218291</t>
+          <t>221140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>341709</t>
+          <t>342958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>405152</t>
+          <t>408998</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196780</t>
+          <t>196502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247383</t>
+          <t>248867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195276</t>
+          <t>195315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242594</t>
+          <t>241839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410078</t>
+          <t>405595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>475059</t>
+          <t>475400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120943</t>
+          <t>124790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>167647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114553</t>
+          <t>113116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155008</t>
+          <t>155311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249089</t>
+          <t>250534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308046</t>
+          <t>314714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1201334</t>
+          <t>1204112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1310130</t>
+          <t>1317310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1349259</t>
+          <t>1345496</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1465325</t>
+          <t>1460742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2585730</t>
+          <t>2577794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2746272</t>
+          <t>2743207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1276421</t>
+          <t>1268996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1390836</t>
+          <t>1384371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1289638</t>
+          <t>1286011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1411517</t>
+          <t>1411311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2605280</t>
+          <t>2591583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2765041</t>
+          <t>2762082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>727251</t>
+          <t>726872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>827426</t>
+          <t>827806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>714665</t>
+          <t>719483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>814041</t>
+          <t>815090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1474360</t>
+          <t>1473182</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1607125</t>
+          <t>1615288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55449</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>48251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69584</t>
+          <t>76946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,67 +6928,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57287</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69543</t>
+          <t>76548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>125127</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>106358</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>143844</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>7,62%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>112736</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>95427</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>130813</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68825</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119278</t>
+          <t>131576</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105048</t>
+          <t>112964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135161</t>
+          <t>147895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>174176</t>
+          <t>197743</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154784</t>
+          <t>176834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195750</t>
+          <t>225119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>403572</t>
+          <t>449919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>385382</t>
+          <t>429529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>419159</t>
+          <t>469961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>574904</t>
+          <t>622450</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>555837</t>
+          <t>603002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>592930</t>
+          <t>641234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>978475</t>
+          <t>1072369</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>953413</t>
+          <t>1045347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1003097</t>
+          <t>1099705</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>751470</t>
+          <t>817795</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>751470</t>
+          <t>817795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>751470</t>
+          <t>817795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1265388</t>
+          <t>1395239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1265388</t>
+          <t>1395239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1265388</t>
+          <t>1395239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>137589</t>
+          <t>153047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95929</t>
+          <t>126629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171183</t>
+          <t>183757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373771</t>
+          <t>190180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175277</t>
+          <t>166082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>826203</t>
+          <t>216974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>511360</t>
+          <t>343227</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>301558</t>
+          <t>304745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1169920</t>
+          <t>377272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>253812</t>
+          <t>276464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176854</t>
+          <t>241786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>306202</t>
+          <t>312744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>318010</t>
+          <t>291520</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>229511</t>
+          <t>263493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>519425</t>
+          <t>323835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>571821</t>
+          <t>567985</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>460679</t>
+          <t>525011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>785723</t>
+          <t>616673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1898926</t>
+          <t>1801055</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1831077</t>
+          <t>1757282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2018253</t>
+          <t>1844963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1546043</t>
+          <t>1689692</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1099309</t>
+          <t>1651266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1738608</t>
+          <t>1723977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3444969</t>
+          <t>3490748</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2925799</t>
+          <t>3433916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3673477</t>
+          <t>3546600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,22 +7805,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92468</t>
+          <t>101879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>88653</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65245</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95824</t>
+          <t>105998</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>152780</t>
+          <t>168783</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131163</t>
+          <t>146419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>177939</t>
+          <t>194064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>108260</t>
+          <t>123020</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132744</t>
+          <t>147697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97518</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81905</t>
+          <t>96011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113837</t>
+          <t>131601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>205778</t>
+          <t>235597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179398</t>
+          <t>208335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232848</t>
+          <t>264109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>464587</t>
+          <t>508014</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>438720</t>
+          <t>478332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488169</t>
+          <t>533613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>481606</t>
+          <t>530785</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461326</t>
+          <t>509474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501151</t>
+          <t>553091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>946193</t>
+          <t>1038800</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915510</t>
+          <t>1001784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>977571</t>
+          <t>1071469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646223</t>
+          <t>711163</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646223</t>
+          <t>711163</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646223</t>
+          <t>711163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658528</t>
+          <t>732015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658528</t>
+          <t>732015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658528</t>
+          <t>732015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1304751</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1304751</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1304751</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>266414</t>
+          <t>294534</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205458</t>
+          <t>261945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>307743</t>
+          <t>332929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>510462</t>
+          <t>342602</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316381</t>
+          <t>311730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1205504</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>776876</t>
+          <t>637136</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>566079</t>
+          <t>589848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1452015</t>
+          <t>684875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>416970</t>
+          <t>465651</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324401</t>
+          <t>421213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467559</t>
+          <t>510911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>534806</t>
+          <t>535673</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451800</t>
+          <t>494578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761253</t>
+          <t>572007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>951776</t>
+          <t>1001324</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836450</t>
+          <t>942466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1152443</t>
+          <t>1059274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2767085</t>
+          <t>2758988</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2696452</t>
+          <t>2703079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2932636</t>
+          <t>2807940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2602553</t>
+          <t>2842928</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2056461</t>
+          <t>2801994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2806062</t>
+          <t>2892745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5369638</t>
+          <t>5601916</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4816256</t>
+          <t>5533143</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5593246</t>
+          <t>5675416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450469</t>
+          <t>3519173</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450469</t>
+          <t>3519173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450469</t>
+          <t>3519173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3647821</t>
+          <t>3721203</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3647821</t>
+          <t>3721203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3647821</t>
+          <t>3721203</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7098290</t>
+          <t>7240376</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7098290</t>
+          <t>7240376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7098290</t>
+          <t>7240376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
